--- a/data/trans_orig/Q33-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según las horas al día que duerme habitualmente</t>
+          <t>Población según las horas al día que duerme habitualmente (tasa de respuesta: 98,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,27 +716,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 7,8</t>
+          <t>7,56; 7,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,53</t>
+          <t>7,2; 7,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>7,01; 7,34</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>7,03; 7,35</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7,02; 7,37</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,58</t>
+          <t>7,31; 7,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,22 +746,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,2</t>
+          <t>6,85; 7,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,04</t>
+          <t>6,83; 7,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 7,66</t>
+          <t>7,47; 7,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,31</t>
+          <t>7,08; 7,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,18</t>
+          <t>6,97; 7,18</t>
         </is>
       </c>
     </row>
@@ -861,27 +861,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,6</t>
+          <t>7,31; 7,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,51</t>
+          <t>7,31; 7,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,43</t>
+          <t>7,16; 7,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,31</t>
+          <t>7,07; 7,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,42</t>
+          <t>7,16; 7,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,38</t>
+          <t>7,18; 7,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,37</t>
+          <t>7,21; 7,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,47</t>
+          <t>7,27; 7,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,32</t>
+          <t>7,17; 7,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,75</t>
+          <t>7,55; 7,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,62</t>
+          <t>7,3; 7,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,23</t>
+          <t>6,99; 7,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 7,4</t>
+          <t>7,14; 7,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,06</t>
+          <t>6,84; 7,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,55</t>
+          <t>7,39; 7,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,46</t>
+          <t>7,26; 7,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,41</t>
+          <t>7,27; 7,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,12</t>
+          <t>6,95; 7,11</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,54</t>
+          <t>7,34; 7,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,31</t>
+          <t>7,01; 7,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,31</t>
+          <t>7,02; 7,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,25</t>
+          <t>6,91; 7,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,46</t>
+          <t>7,27; 7,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 6,97</t>
+          <t>6,66; 6,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 7,16</t>
+          <t>6,81; 7,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,06</t>
+          <t>6,84; 7,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,48</t>
+          <t>7,32; 7,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,09</t>
+          <t>6,88; 7,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,17</t>
+          <t>6,96; 7,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,11</t>
+          <t>6,92; 7,1</t>
         </is>
       </c>
     </row>
@@ -1281,27 +1281,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,52</t>
+          <t>7,17; 7,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,64</t>
+          <t>7,44; 7,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,68; 6,92</t>
+          <t>6,67; 6,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,8</t>
+          <t>7,43; 7,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,26</t>
+          <t>6,86; 7,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 6,66</t>
+          <t>6,48; 6,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 7,72</t>
+          <t>7,48; 7,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,33</t>
+          <t>7,07; 7,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 7,63</t>
+          <t>7,48; 7,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,51</t>
+          <t>7,25; 7,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,66</t>
+          <t>7,35; 7,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,15</t>
+          <t>6,93; 7,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,22 +1441,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,37</t>
+          <t>7,07; 7,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,32</t>
+          <t>6,98; 7,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 6,95</t>
+          <t>6,7; 6,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,51</t>
+          <t>7,33; 7,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,03</t>
+          <t>6,86; 7,02</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,69</t>
+          <t>7,51; 7,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1566,52 +1566,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,76</t>
+          <t>7,55; 7,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,08</t>
+          <t>6,88; 7,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,44</t>
+          <t>7,24; 7,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,31</t>
+          <t>7,12; 7,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,54</t>
+          <t>7,35; 7,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 6,93</t>
+          <t>6,35; 6,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,53</t>
+          <t>7,41; 7,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,36</t>
+          <t>7,21; 7,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 7,62</t>
+          <t>7,48; 7,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 6,96</t>
+          <t>6,51; 6,96</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,59</t>
+          <t>7,42; 7,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,58</t>
+          <t>7,41; 7,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 8,5</t>
+          <t>7,43; 8,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,68</t>
+          <t>7,52; 7,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,41</t>
+          <t>7,25; 7,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,46</t>
+          <t>7,33; 7,45</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,16</t>
+          <t>7,38; 8,14</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,51</t>
+          <t>7,42; 7,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,69</t>
+          <t>7,15; 7,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,23</t>
+          <t>7,13; 7,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,29</t>
+          <t>7,2; 7,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,05</t>
+          <t>6,78; 7,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,31</t>
+          <t>7,25; 7,32</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,34</t>
+          <t>7,03; 7,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q33-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Provincia-trans_orig.xlsx
@@ -663,39 +663,39 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>7,16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,46</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,02</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,02</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7,01</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7,57</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>7,19</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,46</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,02</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,02</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6,94</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,57</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>7,1</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,08</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 7,82</t>
+          <t>7,56; 7,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,51</t>
+          <t>7,19; 7,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,34</t>
+          <t>7,0; 7,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,35</t>
+          <t>7,03; 7,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,6</t>
+          <t>7,3; 7,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,2</t>
+          <t>6,84; 7,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,2</t>
+          <t>6,84; 7,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,04</t>
+          <t>6,9; 7,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 7,67</t>
+          <t>7,47; 7,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,32</t>
+          <t>7,06; 7,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,23</t>
+          <t>6,98; 7,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,18</t>
+          <t>7,0; 7,17</t>
         </is>
       </c>
     </row>
@@ -803,47 +803,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>7,3</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,18</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>7,29</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,18</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,08</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7,27</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7,29</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,08</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,28</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7,37</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7,24</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,29</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7,37</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,28</t>
         </is>
       </c>
     </row>
@@ -861,57 +861,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,59</t>
+          <t>7,32; 7,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,51</t>
+          <t>7,31; 7,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,44</t>
+          <t>7,17; 7,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,31</t>
+          <t>7,06; 7,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,42</t>
+          <t>7,18; 7,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,2</t>
+          <t>6,98; 7,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,41</t>
+          <t>7,17; 7,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t>7,2; 7,37</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7,28; 7,45</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7,16; 7,32</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>7,21; 7,37</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7,27; 7,46</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7,17; 7,32</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,2; 7,37</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>6,94</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>7,01</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,55; 7,75</t>
+          <t>7,54; 7,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,64</t>
+          <t>7,3; 7,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,51</t>
+          <t>7,33; 7,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,24</t>
+          <t>6,94; 7,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,42</t>
+          <t>7,19; 7,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,41</t>
+          <t>7,14; 7,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,36</t>
+          <t>7,14; 7,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,07</t>
+          <t>6,83; 7,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,55</t>
+          <t>7,4; 7,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,45</t>
+          <t>7,26; 7,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,42</t>
+          <t>7,27; 7,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,11</t>
+          <t>6,92; 7,09</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,54</t>
+          <t>7,33; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,3</t>
+          <t>7,02; 7,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,32</t>
+          <t>7,03; 7,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,24</t>
+          <t>6,91; 7,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,46</t>
+          <t>7,26; 7,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 6,98</t>
+          <t>6,66; 6,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 7,14</t>
+          <t>6,83; 7,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,07</t>
+          <t>6,83; 7,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,48</t>
+          <t>7,33; 7,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,09</t>
+          <t>6,87; 7,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,19</t>
+          <t>6,97; 7,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,1</t>
+          <t>6,91; 7,12</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,56</t>
+          <t>6,57</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,69</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,79</t>
+          <t>7,44; 7,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,54</t>
+          <t>7,16; 7,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 7,65</t>
+          <t>7,43; 7,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 6,92</t>
+          <t>6,71; 6,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,78</t>
+          <t>7,41; 7,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,26</t>
+          <t>6,88; 7,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 7,67</t>
+          <t>7,47; 7,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 6,67</t>
+          <t>6,48; 6,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 7,74</t>
+          <t>7,49; 7,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 6,75</t>
+          <t>6,62; 6,76</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>6,93</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,48; 7,7</t>
+          <t>7,49; 7,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1426,52 +1426,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,65</t>
+          <t>7,37; 7,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,16</t>
+          <t>6,91; 7,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,37</t>
+          <t>7,1; 7,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,38</t>
+          <t>7,06; 7,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,32</t>
+          <t>7,02; 7,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,7; 6,95</t>
+          <t>6,7; 6,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,5</t>
+          <t>7,32; 7,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,41</t>
+          <t>7,21; 7,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,45</t>
+          <t>7,22; 7,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,02</t>
+          <t>6,84; 7,01</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,68</t>
+          <t>6,9</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>6,95</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,67</t>
+          <t>7,52; 7,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,45</t>
+          <t>7,28; 7,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 7,76</t>
+          <t>7,55; 7,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,1</t>
+          <t>6,92; 7,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,44</t>
+          <t>7,24; 7,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,31</t>
+          <t>7,11; 7,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,55</t>
+          <t>7,35; 7,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,35; 6,94</t>
+          <t>6,82; 6,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,53</t>
+          <t>7,4; 7,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,35</t>
+          <t>7,22; 7,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,48; 7,63</t>
+          <t>7,47; 7,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 6,96</t>
+          <t>6,89; 7,02</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>7,41</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,6</t>
+          <t>7,42; 7,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,59</t>
+          <t>7,4; 7,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,22 +1711,22 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,48</t>
+          <t>7,41; 7,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,7</t>
+          <t>7,5; 7,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,38</t>
+          <t>7,21; 7,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,41</t>
+          <t>7,26; 7,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,62</t>
+          <t>7,49; 7,61</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,14</t>
+          <t>7,36; 7,45</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,3</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,11</t>
         </is>
       </c>
     </row>
@@ -1841,17 +1841,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,44</t>
+          <t>7,35; 7,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,51</t>
+          <t>7,43; 7,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,66</t>
+          <t>7,13; 7,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1861,37 +1861,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,13; 7,23</t>
+          <t>7,14; 7,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,29</t>
+          <t>7,21; 7,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,78; 7,05</t>
+          <t>7,01; 7,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,44; 7,49</t>
+          <t>7,43; 7,49</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,32</t>
+          <t>7,26; 7,32</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,39</t>
+          <t>7,32; 7,39</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,36</t>
+          <t>7,08; 7,13</t>
         </is>
       </c>
     </row>
